--- a/部門名單.xlsx
+++ b/部門名單.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/idahuang/Downloads/cathay-202604/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14492593-69EC-E043-9A39-99158BD224C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A3847E-E48C-474D-B885-37D313FAA7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="740" windowWidth="28260" windowHeight="16860" xr2:uid="{2625BAFD-72EA-9C4A-BF2A-1D460FAD767F}"/>
+    <workbookView xWindow="1140" yWindow="740" windowWidth="28260" windowHeight="16860" xr2:uid="{2625BAFD-72EA-9C4A-BF2A-1D460FAD767F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="140">
   <si>
     <t>行編</t>
   </si>
@@ -76,13 +76,7 @@
     <t>經辦業務</t>
   </si>
   <si>
-    <t>協理</t>
-  </si>
-  <si>
     <t>專案協理</t>
-  </si>
-  <si>
-    <t>顏勝豪</t>
   </si>
   <si>
     <t>鄒明良</t>
@@ -836,7 +830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{464DE28B-BA9A-8844-9753-2372386C9799}">
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -873,13 +867,13 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1">
-        <v>30875</v>
+        <v>84037</v>
       </c>
       <c r="B2" s="1">
-        <v>530875</v>
+        <v>584037</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>10</v>
@@ -897,7 +891,7 @@
         <v>287936999</v>
       </c>
       <c r="I2" s="2">
-        <v>46037</v>
+        <v>43255</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>12</v>
@@ -905,31 +899,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1">
-        <v>84037</v>
+        <v>1733</v>
       </c>
       <c r="B3" s="1">
-        <v>584037</v>
+        <v>501733</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="H3" s="1">
         <v>287936999</v>
       </c>
       <c r="I3" s="2">
-        <v>43255</v>
+        <v>46037</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>12</v>
@@ -937,10 +931,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1">
-        <v>1733</v>
+        <v>83392</v>
       </c>
       <c r="B4" s="1">
-        <v>501733</v>
+        <v>583392</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>17</v>
@@ -952,10 +946,10 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" s="1">
         <v>287936999</v>
@@ -969,13 +963,13 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1">
-        <v>83392</v>
+        <v>91324</v>
       </c>
       <c r="B5" s="1">
-        <v>583392</v>
+        <v>591324</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>10</v>
@@ -984,7 +978,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>21</v>
@@ -1001,10 +995,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1">
-        <v>91324</v>
+        <v>90779</v>
       </c>
       <c r="B6" s="1">
-        <v>591324</v>
+        <v>590779</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>22</v>
@@ -1016,7 +1010,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>23</v>
@@ -1033,10 +1027,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1">
-        <v>90779</v>
+        <v>98887</v>
       </c>
       <c r="B7" s="1">
-        <v>590779</v>
+        <v>598887</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>24</v>
@@ -1048,7 +1042,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>25</v>
@@ -1065,25 +1059,25 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1">
-        <v>98887</v>
+        <v>90775</v>
       </c>
       <c r="B8" s="1">
-        <v>598887</v>
+        <v>590775</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H8" s="1">
         <v>287936999</v>
@@ -1097,25 +1091,25 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="1">
-        <v>90775</v>
+        <v>92311</v>
       </c>
       <c r="B9" s="1">
-        <v>590775</v>
+        <v>592311</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H9" s="1">
         <v>287936999</v>
@@ -1129,25 +1123,25 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="1">
-        <v>92311</v>
+        <v>97734</v>
       </c>
       <c r="B10" s="1">
-        <v>592311</v>
+        <v>597734</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H10" s="1">
         <v>287936999</v>
@@ -1161,13 +1155,13 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="1">
-        <v>97734</v>
+        <v>95964</v>
       </c>
       <c r="B11" s="1">
-        <v>597734</v>
+        <v>595964</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
@@ -1176,10 +1170,10 @@
         <v>11</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H11" s="1">
         <v>287936999</v>
@@ -1193,13 +1187,13 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="1">
-        <v>95964</v>
+        <v>96631</v>
       </c>
       <c r="B12" s="1">
-        <v>595964</v>
+        <v>596631</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>10</v>
@@ -1208,10 +1202,10 @@
         <v>11</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H12" s="1">
         <v>287936999</v>
@@ -1225,13 +1219,13 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="1">
-        <v>96631</v>
+        <v>96634</v>
       </c>
       <c r="B13" s="1">
-        <v>596631</v>
+        <v>596634</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>10</v>
@@ -1240,10 +1234,10 @@
         <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H13" s="1">
         <v>287936999</v>
@@ -1257,25 +1251,25 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="1">
-        <v>96634</v>
+        <v>98296</v>
       </c>
       <c r="B14" s="1">
-        <v>596634</v>
+        <v>598296</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H14" s="1">
         <v>287936999</v>
@@ -1289,25 +1283,25 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="1">
-        <v>98296</v>
+        <v>96647</v>
       </c>
       <c r="B15" s="1">
-        <v>598296</v>
+        <v>596647</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H15" s="1">
         <v>287936999</v>
@@ -1321,25 +1315,25 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="1">
-        <v>96647</v>
+        <v>96637</v>
       </c>
       <c r="B16" s="1">
-        <v>596647</v>
+        <v>596637</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H16" s="1">
         <v>287936999</v>
@@ -1353,25 +1347,25 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="1">
-        <v>96637</v>
+        <v>99242</v>
       </c>
       <c r="B17" s="1">
-        <v>596637</v>
+        <v>599242</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="H17" s="1">
         <v>287936999</v>
@@ -1385,10 +1379,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="1">
-        <v>99242</v>
+        <v>98297</v>
       </c>
       <c r="B18" s="1">
-        <v>599242</v>
+        <v>598297</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>37</v>
@@ -1400,10 +1394,10 @@
         <v>11</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H18" s="1">
         <v>287936999</v>
@@ -1417,13 +1411,13 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="1">
-        <v>98297</v>
+        <v>98302</v>
       </c>
       <c r="B19" s="1">
-        <v>598297</v>
+        <v>598302</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>10</v>
@@ -1432,10 +1426,10 @@
         <v>11</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H19" s="1">
         <v>287936999</v>
@@ -1449,25 +1443,25 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="1">
-        <v>98302</v>
+        <v>99023</v>
       </c>
       <c r="B20" s="1">
-        <v>598302</v>
+        <v>599023</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H20" s="1">
         <v>287936999</v>
@@ -1481,25 +1475,25 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="1">
-        <v>99023</v>
+        <v>98277</v>
       </c>
       <c r="B21" s="1">
-        <v>599023</v>
+        <v>598277</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H21" s="1">
         <v>287936999</v>
@@ -1513,25 +1507,25 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="1">
-        <v>98277</v>
+        <v>98292</v>
       </c>
       <c r="B22" s="1">
-        <v>598277</v>
+        <v>598292</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H22" s="1">
         <v>287936999</v>
@@ -1545,13 +1539,13 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="1">
-        <v>98292</v>
+        <v>98294</v>
       </c>
       <c r="B23" s="1">
-        <v>598292</v>
+        <v>598294</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>10</v>
@@ -1560,10 +1554,10 @@
         <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H23" s="1">
         <v>287936999</v>
@@ -1577,25 +1571,25 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="1">
-        <v>98294</v>
+        <v>98300</v>
       </c>
       <c r="B24" s="1">
-        <v>598294</v>
+        <v>598300</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H24" s="1">
         <v>287936999</v>
@@ -1609,25 +1603,25 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="1">
-        <v>98300</v>
+        <v>84610</v>
       </c>
       <c r="B25" s="1">
-        <v>598300</v>
+        <v>584610</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="G25" s="1" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="H25" s="1">
         <v>287936999</v>
@@ -1641,10 +1635,10 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="1">
-        <v>84610</v>
+        <v>87906</v>
       </c>
       <c r="B26" s="1">
-        <v>584610</v>
+        <v>587906</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>46</v>
@@ -1656,7 +1650,7 @@
         <v>11</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>21</v>
@@ -1673,13 +1667,13 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="1">
-        <v>87906</v>
+        <v>85510</v>
       </c>
       <c r="B27" s="1">
-        <v>587906</v>
+        <v>585510</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>10</v>
@@ -1688,10 +1682,10 @@
         <v>11</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H27" s="1">
         <v>287936999</v>
@@ -1705,28 +1699,28 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="1">
-        <v>85510</v>
+        <v>92022</v>
       </c>
       <c r="B28" s="1">
-        <v>585510</v>
+        <v>592022</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="1">
-        <v>287936999</v>
+        <v>287936669</v>
       </c>
       <c r="I28" s="2">
         <v>46037</v>
@@ -1737,28 +1731,28 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="1">
-        <v>92022</v>
+        <v>88854</v>
       </c>
       <c r="B29" s="1">
-        <v>592022</v>
+        <v>588854</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H29" s="1">
-        <v>287936669</v>
+        <v>287936999</v>
       </c>
       <c r="I29" s="2">
         <v>46037</v>
@@ -1769,25 +1763,25 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="1">
-        <v>88854</v>
+        <v>82758</v>
       </c>
       <c r="B30" s="1">
-        <v>588854</v>
+        <v>582758</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H30" s="1">
         <v>287936999</v>
@@ -1801,25 +1795,25 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="1">
-        <v>82758</v>
+        <v>87195</v>
       </c>
       <c r="B31" s="1">
-        <v>582758</v>
+        <v>587195</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H31" s="1">
         <v>287936999</v>
@@ -1833,22 +1827,22 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="1">
-        <v>87195</v>
+        <v>99001</v>
       </c>
       <c r="B32" s="1">
-        <v>587195</v>
+        <v>599001</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>25</v>
@@ -1865,13 +1859,13 @@
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="1">
-        <v>99001</v>
+        <v>99253</v>
       </c>
       <c r="B33" s="1">
-        <v>599001</v>
+        <v>599253</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>10</v>
@@ -1880,13 +1874,13 @@
         <v>11</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H33" s="1">
-        <v>287936999</v>
+        <v>287226666</v>
       </c>
       <c r="I33" s="2">
         <v>46037</v>
@@ -1897,13 +1891,13 @@
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="1">
-        <v>99253</v>
+        <v>94229</v>
       </c>
       <c r="B34" s="1">
-        <v>599253</v>
+        <v>594229</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>10</v>
@@ -1912,13 +1906,13 @@
         <v>11</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H34" s="1">
-        <v>287226666</v>
+        <v>287936999</v>
       </c>
       <c r="I34" s="2">
         <v>46037</v>
@@ -1929,25 +1923,25 @@
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="1">
-        <v>94229</v>
+        <v>92235</v>
       </c>
       <c r="B35" s="1">
-        <v>594229</v>
+        <v>592235</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H35" s="1">
         <v>287936999</v>
@@ -1961,25 +1955,25 @@
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="1">
-        <v>92235</v>
+        <v>92282</v>
       </c>
       <c r="B36" s="1">
-        <v>592235</v>
+        <v>592282</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H36" s="1">
         <v>287936999</v>
@@ -1993,13 +1987,13 @@
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="1">
-        <v>92282</v>
+        <v>96744</v>
       </c>
       <c r="B37" s="1">
-        <v>592282</v>
+        <v>596744</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>10</v>
@@ -2008,10 +2002,10 @@
         <v>11</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H37" s="1">
         <v>287936999</v>
@@ -2025,13 +2019,13 @@
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="1">
-        <v>96744</v>
+        <v>94411</v>
       </c>
       <c r="B38" s="1">
-        <v>596744</v>
+        <v>594411</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>10</v>
@@ -2040,10 +2034,10 @@
         <v>11</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H38" s="1">
         <v>287936999</v>
@@ -2057,25 +2051,25 @@
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="1">
-        <v>94411</v>
+        <v>91609</v>
       </c>
       <c r="B39" s="1">
-        <v>594411</v>
+        <v>591609</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H39" s="1">
         <v>287936999</v>
@@ -2089,25 +2083,25 @@
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="1">
-        <v>91609</v>
+        <v>96350</v>
       </c>
       <c r="B40" s="1">
-        <v>591609</v>
+        <v>596350</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H40" s="1">
         <v>287936999</v>
@@ -2121,25 +2115,25 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="1">
-        <v>96350</v>
+        <v>98981</v>
       </c>
       <c r="B41" s="1">
-        <v>596350</v>
+        <v>598981</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="G41" s="1" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="H41" s="1">
         <v>287936999</v>
@@ -2152,47 +2146,47 @@
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="1">
-        <v>98981</v>
+      <c r="A42" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="B42" s="1">
-        <v>598981</v>
+        <v>500000</v>
       </c>
       <c r="C42" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G42" s="1" t="s">
+      <c r="H42" s="1">
+        <v>287936999</v>
+      </c>
+      <c r="I42" s="2">
+        <v>46037</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="1">
+        <v>48035</v>
+      </c>
+      <c r="B43" s="1">
+        <v>548035</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H42" s="1">
-        <v>287936999</v>
-      </c>
-      <c r="I42" s="2">
-        <v>46037</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B43" s="1">
-        <v>500000</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="D43" s="1" t="s">
         <v>10</v>
       </c>
@@ -2200,10 +2194,10 @@
         <v>11</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="H43" s="1">
         <v>287936999</v>
@@ -2217,13 +2211,13 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="1">
-        <v>48035</v>
+        <v>87982</v>
       </c>
       <c r="B44" s="1">
-        <v>548035</v>
+        <v>587982</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>10</v>
@@ -2232,7 +2226,7 @@
         <v>11</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>23</v>
@@ -2249,13 +2243,13 @@
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="1">
-        <v>87982</v>
+        <v>91907</v>
       </c>
       <c r="B45" s="1">
-        <v>587982</v>
+        <v>591907</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>10</v>
@@ -2264,10 +2258,10 @@
         <v>11</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H45" s="1">
         <v>287936999</v>
@@ -2281,13 +2275,13 @@
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="1">
-        <v>91907</v>
+        <v>81364</v>
       </c>
       <c r="B46" s="1">
-        <v>591907</v>
+        <v>581364</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>10</v>
@@ -2296,10 +2290,10 @@
         <v>11</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H46" s="1">
         <v>287936999</v>
@@ -2313,13 +2307,13 @@
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="1">
-        <v>81364</v>
+        <v>42681</v>
       </c>
       <c r="B47" s="1">
-        <v>581364</v>
+        <v>542681</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>10</v>
@@ -2328,10 +2322,10 @@
         <v>11</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H47" s="1">
         <v>287936999</v>
@@ -2345,13 +2339,13 @@
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="1">
-        <v>42681</v>
+        <v>98882</v>
       </c>
       <c r="B48" s="1">
-        <v>542681</v>
+        <v>598882</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>10</v>
@@ -2360,10 +2354,10 @@
         <v>11</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H48" s="1">
         <v>287936999</v>
@@ -2377,28 +2371,28 @@
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="1">
-        <v>98882</v>
+        <v>94547</v>
       </c>
       <c r="B49" s="1">
-        <v>598882</v>
+        <v>594547</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H49" s="1">
-        <v>287936999</v>
+        <v>287936966</v>
       </c>
       <c r="I49" s="2">
         <v>46037</v>
@@ -2409,28 +2403,28 @@
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="1">
-        <v>94547</v>
+        <v>86807</v>
       </c>
       <c r="B50" s="1">
-        <v>594547</v>
+        <v>586807</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H50" s="1">
-        <v>287936966</v>
+        <v>287936999</v>
       </c>
       <c r="I50" s="2">
         <v>46037</v>
@@ -2441,13 +2435,13 @@
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="1">
-        <v>86807</v>
+        <v>96417</v>
       </c>
       <c r="B51" s="1">
-        <v>586807</v>
+        <v>596417</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>10</v>
@@ -2456,10 +2450,10 @@
         <v>11</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H51" s="1">
         <v>287936999</v>
@@ -2473,25 +2467,25 @@
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="1">
-        <v>96417</v>
+        <v>95559</v>
       </c>
       <c r="B52" s="1">
-        <v>596417</v>
+        <v>595559</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H52" s="1">
         <v>287936999</v>
@@ -2505,25 +2499,25 @@
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="1">
-        <v>95559</v>
+        <v>16403</v>
       </c>
       <c r="B53" s="1">
-        <v>595559</v>
+        <v>516403</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H53" s="1">
         <v>287936999</v>
@@ -2537,13 +2531,13 @@
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="1">
-        <v>16403</v>
+        <v>15438</v>
       </c>
       <c r="B54" s="1">
-        <v>516403</v>
+        <v>515438</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>10</v>
@@ -2552,10 +2546,10 @@
         <v>11</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H54" s="1">
         <v>287936999</v>
@@ -2569,25 +2563,25 @@
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="1">
-        <v>15438</v>
+        <v>94341</v>
       </c>
       <c r="B55" s="1">
-        <v>515438</v>
+        <v>594341</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H55" s="1">
         <v>287936999</v>
@@ -2601,28 +2595,28 @@
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="1">
-        <v>94341</v>
+        <v>30880</v>
       </c>
       <c r="B56" s="1">
-        <v>594341</v>
+        <v>530880</v>
       </c>
       <c r="C56" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="G56" s="1" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="H56" s="1">
-        <v>287936999</v>
+        <v>287226666</v>
       </c>
       <c r="I56" s="2">
         <v>46037</v>
@@ -2633,10 +2627,10 @@
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="1">
-        <v>30880</v>
+        <v>86115</v>
       </c>
       <c r="B57" s="1">
-        <v>530880</v>
+        <v>586115</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>80</v>
@@ -2648,10 +2642,10 @@
         <v>11</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H57" s="1">
         <v>287226666</v>
@@ -2665,13 +2659,13 @@
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="1">
-        <v>86115</v>
+        <v>87730</v>
       </c>
       <c r="B58" s="1">
-        <v>586115</v>
+        <v>587730</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>10</v>
@@ -2680,13 +2674,13 @@
         <v>11</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="H58" s="1">
-        <v>287226666</v>
+        <v>287936999</v>
       </c>
       <c r="I58" s="2">
         <v>46037</v>
@@ -2697,13 +2691,13 @@
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="1">
-        <v>87730</v>
+        <v>87750</v>
       </c>
       <c r="B59" s="1">
-        <v>587730</v>
+        <v>587750</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>10</v>
@@ -2712,10 +2706,10 @@
         <v>11</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H59" s="1">
         <v>287936999</v>
@@ -2729,13 +2723,13 @@
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="1">
-        <v>87750</v>
+        <v>89579</v>
       </c>
       <c r="B60" s="1">
-        <v>587750</v>
+        <v>589579</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>10</v>
@@ -2744,13 +2738,13 @@
         <v>11</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="1">
-        <v>287936999</v>
+        <v>287226666</v>
       </c>
       <c r="I60" s="2">
         <v>46037</v>
@@ -2761,28 +2755,28 @@
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="1">
-        <v>89579</v>
+        <v>84628</v>
       </c>
       <c r="B61" s="1">
-        <v>589579</v>
+        <v>584628</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H61" s="1">
-        <v>287226666</v>
+        <v>287936999</v>
       </c>
       <c r="I61" s="2">
         <v>46037</v>
@@ -2793,25 +2787,25 @@
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="1">
-        <v>84628</v>
+        <v>86596</v>
       </c>
       <c r="B62" s="1">
-        <v>584628</v>
+        <v>586596</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H62" s="1">
         <v>287936999</v>
@@ -2825,25 +2819,25 @@
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="1">
-        <v>86596</v>
+        <v>95736</v>
       </c>
       <c r="B63" s="1">
-        <v>586596</v>
+        <v>595736</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H63" s="1">
         <v>287936999</v>
@@ -2857,13 +2851,13 @@
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="1">
-        <v>95736</v>
+        <v>98355</v>
       </c>
       <c r="B64" s="1">
-        <v>595736</v>
+        <v>598355</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>10</v>
@@ -2872,7 +2866,7 @@
         <v>11</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>25</v>
@@ -2889,25 +2883,25 @@
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="1">
-        <v>98355</v>
+        <v>96300</v>
       </c>
       <c r="B65" s="1">
-        <v>598355</v>
+        <v>596300</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H65" s="1">
         <v>287936999</v>
@@ -2921,25 +2915,25 @@
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="1">
-        <v>96300</v>
+        <v>96594</v>
       </c>
       <c r="B66" s="1">
-        <v>596300</v>
+        <v>596594</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H66" s="1">
         <v>287936999</v>
@@ -2953,13 +2947,13 @@
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="1">
-        <v>96594</v>
+        <v>97308</v>
       </c>
       <c r="B67" s="1">
-        <v>596594</v>
+        <v>597308</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>10</v>
@@ -2968,10 +2962,10 @@
         <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H67" s="1">
         <v>287936999</v>
@@ -2985,25 +2979,25 @@
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="1">
-        <v>97308</v>
+        <v>95946</v>
       </c>
       <c r="B68" s="1">
-        <v>597308</v>
+        <v>595946</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H68" s="1">
         <v>287936999</v>
@@ -3017,25 +3011,25 @@
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="1">
-        <v>95946</v>
+        <v>92313</v>
       </c>
       <c r="B69" s="1">
-        <v>595946</v>
+        <v>592313</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H69" s="1">
         <v>287936999</v>
@@ -3049,13 +3043,13 @@
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="1">
-        <v>92313</v>
+        <v>95970</v>
       </c>
       <c r="B70" s="1">
-        <v>592313</v>
+        <v>595970</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>10</v>
@@ -3064,13 +3058,13 @@
         <v>11</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H70" s="1">
-        <v>287936999</v>
+        <v>287226666</v>
       </c>
       <c r="I70" s="2">
         <v>46037</v>
@@ -3081,13 +3075,13 @@
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="1">
-        <v>95970</v>
+        <v>97949</v>
       </c>
       <c r="B71" s="1">
-        <v>595970</v>
+        <v>597949</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>10</v>
@@ -3096,13 +3090,13 @@
         <v>11</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H71" s="1">
-        <v>287226666</v>
+        <v>287936999</v>
       </c>
       <c r="I71" s="2">
         <v>46037</v>
@@ -3113,13 +3107,13 @@
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="1">
-        <v>97949</v>
+        <v>98127</v>
       </c>
       <c r="B72" s="1">
-        <v>597949</v>
+        <v>598127</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>10</v>
@@ -3128,10 +3122,10 @@
         <v>11</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H72" s="1">
         <v>287936999</v>
@@ -3145,13 +3139,13 @@
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="1">
-        <v>98127</v>
+        <v>99022</v>
       </c>
       <c r="B73" s="1">
-        <v>598127</v>
+        <v>599022</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>10</v>
@@ -3160,10 +3154,10 @@
         <v>11</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H73" s="1">
         <v>287936999</v>
@@ -3177,25 +3171,25 @@
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="1">
-        <v>99022</v>
+        <v>87053</v>
       </c>
       <c r="B74" s="1">
-        <v>599022</v>
+        <v>587053</v>
       </c>
       <c r="C74" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="G74" s="1" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="H74" s="1">
         <v>287936999</v>
@@ -3209,25 +3203,25 @@
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="1">
-        <v>87053</v>
+        <v>94667</v>
       </c>
       <c r="B75" s="1">
-        <v>587053</v>
+        <v>594667</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>99</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H75" s="1">
         <v>287936999</v>
@@ -3241,25 +3235,25 @@
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="1">
-        <v>94667</v>
+        <v>99445</v>
       </c>
       <c r="B76" s="1">
-        <v>594667</v>
+        <v>599445</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H76" s="1">
         <v>287936999</v>
@@ -3273,25 +3267,25 @@
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="1">
-        <v>99445</v>
+        <v>94721</v>
       </c>
       <c r="B77" s="1">
-        <v>599445</v>
+        <v>594721</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H77" s="1">
         <v>287936999</v>
@@ -3305,25 +3299,25 @@
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="1">
-        <v>94721</v>
+        <v>94132</v>
       </c>
       <c r="B78" s="1">
-        <v>594721</v>
+        <v>594132</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H78" s="1">
         <v>287936999</v>
@@ -3337,25 +3331,25 @@
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="1">
-        <v>94132</v>
+        <v>98287</v>
       </c>
       <c r="B79" s="1">
-        <v>594132</v>
+        <v>598287</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H79" s="1">
         <v>287936999</v>
@@ -3369,25 +3363,25 @@
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="1">
-        <v>98287</v>
+        <v>99396</v>
       </c>
       <c r="B80" s="1">
-        <v>598287</v>
+        <v>599396</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H80" s="1">
         <v>287936999</v>
@@ -3401,25 +3395,25 @@
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="1">
-        <v>99396</v>
+        <v>98414</v>
       </c>
       <c r="B81" s="1">
-        <v>599396</v>
+        <v>598414</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H81" s="1">
         <v>287936999</v>
@@ -3433,25 +3427,25 @@
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="1">
-        <v>98414</v>
+        <v>98422</v>
       </c>
       <c r="B82" s="1">
-        <v>598414</v>
+        <v>598422</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H82" s="1">
         <v>287936999</v>
@@ -3465,13 +3459,13 @@
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="1">
-        <v>98422</v>
+        <v>98423</v>
       </c>
       <c r="B83" s="1">
-        <v>598422</v>
+        <v>598423</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>10</v>
@@ -3480,10 +3474,10 @@
         <v>11</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H83" s="1">
         <v>287936999</v>
@@ -3497,25 +3491,25 @@
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="1">
-        <v>98423</v>
+        <v>94471</v>
       </c>
       <c r="B84" s="1">
-        <v>598423</v>
+        <v>594471</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H84" s="1">
         <v>287936999</v>
@@ -3529,25 +3523,25 @@
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="1">
-        <v>94471</v>
+        <v>94414</v>
       </c>
       <c r="B85" s="1">
-        <v>594471</v>
+        <v>594414</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H85" s="1">
         <v>287936999</v>
@@ -3561,25 +3555,25 @@
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="1">
-        <v>94414</v>
+        <v>94438</v>
       </c>
       <c r="B86" s="1">
-        <v>594414</v>
+        <v>594438</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H86" s="1">
         <v>287936999</v>
@@ -3593,25 +3587,25 @@
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="1">
-        <v>94438</v>
+        <v>94851</v>
       </c>
       <c r="B87" s="1">
-        <v>594438</v>
+        <v>594851</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H87" s="1">
         <v>287936999</v>
@@ -3625,25 +3619,25 @@
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="1">
-        <v>94851</v>
+        <v>94004</v>
       </c>
       <c r="B88" s="1">
-        <v>594851</v>
+        <v>594004</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H88" s="1">
         <v>287936999</v>
@@ -3657,25 +3651,25 @@
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="1">
-        <v>94004</v>
+        <v>94021</v>
       </c>
       <c r="B89" s="1">
-        <v>594004</v>
+        <v>594021</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H89" s="1">
         <v>287936999</v>
@@ -3689,25 +3683,25 @@
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="1">
-        <v>94021</v>
+        <v>94119</v>
       </c>
       <c r="B90" s="1">
-        <v>594021</v>
+        <v>594119</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H90" s="1">
         <v>287936999</v>
@@ -3721,25 +3715,25 @@
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="1">
-        <v>94119</v>
+        <v>94855</v>
       </c>
       <c r="B91" s="1">
-        <v>594119</v>
+        <v>594855</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H91" s="1">
         <v>287936999</v>
@@ -3753,13 +3747,13 @@
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="1">
-        <v>94855</v>
+        <v>94596</v>
       </c>
       <c r="B92" s="1">
-        <v>594855</v>
+        <v>594596</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>10</v>
@@ -3768,10 +3762,10 @@
         <v>11</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H92" s="1">
         <v>287936999</v>
@@ -3785,13 +3779,13 @@
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="1">
-        <v>94596</v>
+        <v>94664</v>
       </c>
       <c r="B93" s="1">
-        <v>594596</v>
+        <v>594664</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>10</v>
@@ -3800,10 +3794,10 @@
         <v>11</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H93" s="1">
         <v>287936999</v>
@@ -3817,25 +3811,25 @@
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="1">
-        <v>94664</v>
+        <v>94486</v>
       </c>
       <c r="B94" s="1">
-        <v>594664</v>
+        <v>594486</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H94" s="1">
         <v>287936999</v>
@@ -3849,25 +3843,25 @@
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="1">
-        <v>94486</v>
+        <v>98291</v>
       </c>
       <c r="B95" s="1">
-        <v>594486</v>
+        <v>598291</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H95" s="1">
         <v>287936999</v>
@@ -3881,25 +3875,25 @@
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="1">
-        <v>98291</v>
+        <v>98304</v>
       </c>
       <c r="B96" s="1">
-        <v>598291</v>
+        <v>598304</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H96" s="1">
         <v>287936999</v>
@@ -3913,25 +3907,25 @@
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="1">
-        <v>98304</v>
+        <v>95750</v>
       </c>
       <c r="B97" s="1">
-        <v>598304</v>
+        <v>595750</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H97" s="1">
         <v>287936999</v>
@@ -3945,13 +3939,13 @@
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="1">
-        <v>95750</v>
+        <v>98298</v>
       </c>
       <c r="B98" s="1">
-        <v>595750</v>
+        <v>598298</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>10</v>
@@ -3960,10 +3954,10 @@
         <v>11</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H98" s="1">
         <v>287936999</v>
@@ -3977,13 +3971,13 @@
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="1">
-        <v>98298</v>
+        <v>98282</v>
       </c>
       <c r="B99" s="1">
-        <v>598298</v>
+        <v>598282</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>10</v>
@@ -3992,10 +3986,10 @@
         <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H99" s="1">
         <v>287936999</v>
@@ -4009,25 +4003,25 @@
     </row>
     <row r="100" spans="1:10">
       <c r="A100" s="1">
-        <v>98282</v>
+        <v>98286</v>
       </c>
       <c r="B100" s="1">
-        <v>598282</v>
+        <v>598286</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H100" s="1">
         <v>287936999</v>
@@ -4041,28 +4035,28 @@
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="1">
-        <v>98286</v>
+        <v>9709</v>
       </c>
       <c r="B101" s="1">
-        <v>598286</v>
+        <v>509709</v>
       </c>
       <c r="C101" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D101" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="G101" s="1" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="H101" s="1">
-        <v>287936999</v>
+        <v>287226666</v>
       </c>
       <c r="I101" s="2">
         <v>46037</v>
@@ -4073,10 +4067,10 @@
     </row>
     <row r="102" spans="1:10">
       <c r="A102" s="1">
-        <v>9709</v>
+        <v>88326</v>
       </c>
       <c r="B102" s="1">
-        <v>509709</v>
+        <v>588326</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>129</v>
@@ -4094,7 +4088,7 @@
         <v>21</v>
       </c>
       <c r="H102" s="1">
-        <v>287226666</v>
+        <v>287936999</v>
       </c>
       <c r="I102" s="2">
         <v>46037</v>
@@ -4105,10 +4099,10 @@
     </row>
     <row r="103" spans="1:10">
       <c r="A103" s="1">
-        <v>88326</v>
+        <v>97595</v>
       </c>
       <c r="B103" s="1">
-        <v>588326</v>
+        <v>597595</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>131</v>
@@ -4120,7 +4114,7 @@
         <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>23</v>
@@ -4137,13 +4131,13 @@
     </row>
     <row r="104" spans="1:10">
       <c r="A104" s="1">
-        <v>97595</v>
+        <v>99192</v>
       </c>
       <c r="B104" s="1">
-        <v>597595</v>
+        <v>599192</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>10</v>
@@ -4152,10 +4146,10 @@
         <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H104" s="1">
         <v>287936999</v>
@@ -4169,13 +4163,13 @@
     </row>
     <row r="105" spans="1:10">
       <c r="A105" s="1">
-        <v>99192</v>
+        <v>89114</v>
       </c>
       <c r="B105" s="1">
-        <v>599192</v>
+        <v>589114</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>10</v>
@@ -4184,10 +4178,10 @@
         <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H105" s="1">
         <v>287936999</v>
@@ -4201,13 +4195,13 @@
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="1">
-        <v>89114</v>
+        <v>97787</v>
       </c>
       <c r="B106" s="1">
-        <v>589114</v>
+        <v>597787</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>10</v>
@@ -4216,13 +4210,13 @@
         <v>11</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H106" s="1">
-        <v>287936999</v>
+        <v>287226666</v>
       </c>
       <c r="I106" s="2">
         <v>46037</v>
@@ -4233,13 +4227,13 @@
     </row>
     <row r="107" spans="1:10">
       <c r="A107" s="1">
-        <v>97787</v>
+        <v>95248</v>
       </c>
       <c r="B107" s="1">
-        <v>597787</v>
+        <v>595248</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>10</v>
@@ -4248,13 +4242,13 @@
         <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H107" s="1">
-        <v>287226666</v>
+        <v>287936999</v>
       </c>
       <c r="I107" s="2">
         <v>46037</v>
@@ -4265,13 +4259,13 @@
     </row>
     <row r="108" spans="1:10">
       <c r="A108" s="1">
-        <v>95248</v>
+        <v>96097</v>
       </c>
       <c r="B108" s="1">
-        <v>595248</v>
+        <v>596097</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>10</v>
@@ -4280,10 +4274,10 @@
         <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H108" s="1">
         <v>287936999</v>
@@ -4297,13 +4291,13 @@
     </row>
     <row r="109" spans="1:10">
       <c r="A109" s="1">
-        <v>96097</v>
+        <v>98765</v>
       </c>
       <c r="B109" s="1">
-        <v>596097</v>
+        <v>598765</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>10</v>
@@ -4312,10 +4306,10 @@
         <v>11</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H109" s="1">
         <v>287936999</v>
@@ -4329,13 +4323,13 @@
     </row>
     <row r="110" spans="1:10">
       <c r="A110" s="1">
-        <v>98765</v>
+        <v>95975</v>
       </c>
       <c r="B110" s="1">
-        <v>598765</v>
+        <v>595975</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>10</v>
@@ -4344,10 +4338,10 @@
         <v>11</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H110" s="1">
         <v>287936999</v>
@@ -4361,13 +4355,13 @@
     </row>
     <row r="111" spans="1:10">
       <c r="A111" s="1">
-        <v>95975</v>
+        <v>97950</v>
       </c>
       <c r="B111" s="1">
-        <v>595975</v>
+        <v>597950</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>10</v>
@@ -4376,10 +4370,10 @@
         <v>11</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H111" s="1">
         <v>287936999</v>
@@ -4388,38 +4382,6 @@
         <v>46037</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10">
-      <c r="A112" s="1">
-        <v>97950</v>
-      </c>
-      <c r="B112" s="1">
-        <v>597950</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H112" s="1">
-        <v>287936999</v>
-      </c>
-      <c r="I112" s="2">
-        <v>46037</v>
-      </c>
-      <c r="J112" s="1" t="s">
         <v>12</v>
       </c>
     </row>
